--- a/outputs/262-17.xlsx
+++ b/outputs/262-17.xlsx
@@ -216,60 +216,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -525,287 +529,287 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="7" t="n">
         <v>44774</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>44774</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>44774</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>44805</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <v>44593</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>44805</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>44593</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>44805</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>44571</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>44896</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>44571</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>44835</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>44682</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>44742</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>44571</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>44896</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>44571</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>44835</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>44562</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>44896</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>44562</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>44835</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -842,295 +846,295 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="7" t="n">
         <v>44774</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>44774</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>44774</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>44805</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>44805</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>44593</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>44805</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>44571</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>44896</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>44571</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>44835</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>44682</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>44742</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="10" t="n">
         <v>44571</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>44896</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="10" t="n">
         <v>44571</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>44835</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>44562</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>44896</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>44562</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>44835</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
     </row>
